--- a/data/raw/individual/205/continuous/mHLEA_paper/205_mHLEA_paper_20230904.xlsx
+++ b/data/raw/individual/205/continuous/mHLEA_paper/205_mHLEA_paper_20230904.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cyepi\data\raw\individual\205\continuous\mHLEA_paper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/GuidolinEtAl_Dataset_2025/data/raw/individual/205/continuous/mHLEA_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F094596-E80B-457D-857C-C596F4EB788C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0359A703-245E-A841-83EF-EC87468E6DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="6330" xr2:uid="{C6F67B1F-B066-4BED-911D-8EE21466DFEE}"/>
+    <workbookView xWindow="1160" yWindow="780" windowWidth="31820" windowHeight="18700" xr2:uid="{C6F67B1F-B066-4BED-911D-8EE21466DFEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -58,19 +69,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Courier New"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,14 +98,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -116,9 +120,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -156,7 +160,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -262,7 +266,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -404,7 +408,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -412,15 +416,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6873E474-6AE4-44FC-836F-91CBD888AE07}">
-  <dimension ref="A1:E158"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C158"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -431,40 +434,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45166.5</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45166.541666666664</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45166.583333333336</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="E4" s="3">
-        <f t="shared" ref="E4:E5" si="0">E2 + (ROW()-1)/24</f>
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45166.625</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="E5" s="3">
-        <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45166.666666666664</v>
       </c>
@@ -472,7 +466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45166.708333333336</v>
       </c>
@@ -480,7 +474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45166.75</v>
       </c>
@@ -488,7 +482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45166.791666666664</v>
       </c>
@@ -496,7 +490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>45166.833333333336</v>
       </c>
@@ -504,7 +498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>45166.875</v>
       </c>
@@ -512,7 +506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>45166.916666666664</v>
       </c>
@@ -520,7 +514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>45166.958333333336</v>
       </c>
@@ -528,7 +522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>45167</v>
       </c>
@@ -536,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>45167.041666666664</v>
       </c>
@@ -544,7 +538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>45167.083333333336</v>
       </c>
@@ -552,7 +546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>45167.125</v>
       </c>
@@ -560,7 +554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>45167.166666666664</v>
       </c>
@@ -568,7 +562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>45167.208333333336</v>
       </c>
@@ -579,7 +573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>45167.25</v>
       </c>
@@ -590,7 +584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>45167.291666666664</v>
       </c>
@@ -601,7 +595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>45167.333333333336</v>
       </c>
@@ -612,7 +606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>45167.375</v>
       </c>
@@ -623,7 +617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>45167.416666666664</v>
       </c>
@@ -631,7 +625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>45167.458333333336</v>
       </c>
@@ -639,7 +633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>45167.5</v>
       </c>
@@ -647,7 +641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>45167.541666666664</v>
       </c>
@@ -655,7 +649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>45167.583333333336</v>
       </c>
@@ -666,7 +660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>45167.625</v>
       </c>
@@ -674,7 +668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>45167.666666666664</v>
       </c>
@@ -682,7 +676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>45167.708333333336</v>
       </c>
@@ -690,7 +684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>45167.75</v>
       </c>
@@ -698,7 +692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>45167.791666666664</v>
       </c>
@@ -706,7 +700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>45167.833333333336</v>
       </c>
@@ -714,7 +708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>45167.875</v>
       </c>
@@ -722,7 +716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>45167.916666666664</v>
       </c>
@@ -730,7 +724,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>45167.958333333336</v>
       </c>
@@ -738,7 +732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>45168</v>
       </c>
@@ -746,7 +740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>45168.041666666664</v>
       </c>
@@ -754,7 +748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>45168.08333321759</v>
       </c>
@@ -762,7 +756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>45168.124999826388</v>
       </c>
@@ -770,7 +764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>45168.166666435187</v>
       </c>
@@ -778,7 +772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>45168.208333043978</v>
       </c>
@@ -789,7 +783,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>45168.249999652777</v>
       </c>
@@ -800,7 +794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>45168.291666261575</v>
       </c>
@@ -811,7 +805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45168.333332870374</v>
       </c>
@@ -822,7 +816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45168.374999479165</v>
       </c>
@@ -833,7 +827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>45168.416666087964</v>
       </c>
@@ -841,7 +835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45168.458332696762</v>
       </c>
@@ -849,7 +843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>45168.499999305554</v>
       </c>
@@ -857,7 +851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>45168.541665914352</v>
       </c>
@@ -865,7 +859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>45168.583332523151</v>
       </c>
@@ -873,7 +867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>45168.624999131942</v>
       </c>
@@ -881,7 +875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>45168.66666574074</v>
       </c>
@@ -889,7 +883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>45168.708332349539</v>
       </c>
@@ -897,7 +891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>45168.74999895833</v>
       </c>
@@ -905,7 +899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>45168.791665567129</v>
       </c>
@@ -913,7 +907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>45168.833332175927</v>
       </c>
@@ -921,7 +915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>45168.874998784719</v>
       </c>
@@ -929,7 +923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>45168.916665393517</v>
       </c>
@@ -937,7 +931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>45168.958332002316</v>
       </c>
@@ -945,7 +939,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>45168.999998611114</v>
       </c>
@@ -953,7 +947,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>45169.041665219906</v>
       </c>
@@ -961,7 +955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>45169.083331828704</v>
       </c>
@@ -969,7 +963,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>45169.124998437503</v>
       </c>
@@ -977,7 +971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>45169.166665046294</v>
       </c>
@@ -985,7 +979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>45169.208331655092</v>
       </c>
@@ -993,7 +987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>45169.249998263891</v>
       </c>
@@ -1001,7 +995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>45169.291664872682</v>
       </c>
@@ -1009,7 +1003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>45169.333331481481</v>
       </c>
@@ -1017,7 +1011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>45169.374998090279</v>
       </c>
@@ -1025,7 +1019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>45169.416664699071</v>
       </c>
@@ -1033,7 +1027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>45169.458331307869</v>
       </c>
@@ -1041,7 +1035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>45169.499997916668</v>
       </c>
@@ -1049,7 +1043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>45169.541664525466</v>
       </c>
@@ -1057,7 +1051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>45169.583331134258</v>
       </c>
@@ -1065,7 +1059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>45169.624997743056</v>
       </c>
@@ -1073,7 +1067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>45169.666664351855</v>
       </c>
@@ -1081,7 +1075,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>45169.708330960646</v>
       </c>
@@ -1089,7 +1083,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>45169.749997569445</v>
       </c>
@@ -1097,7 +1091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>45169.791664178243</v>
       </c>
@@ -1105,7 +1099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>45169.833330787034</v>
       </c>
@@ -1113,7 +1107,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>45169.874997395833</v>
       </c>
@@ -1121,7 +1115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>45169.916664004631</v>
       </c>
@@ -1129,7 +1123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>45169.958330613423</v>
       </c>
@@ -1137,7 +1131,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>45169.999997222221</v>
       </c>
@@ -1145,7 +1139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>45170.04166383102</v>
       </c>
@@ -1153,7 +1147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>45170.083330439818</v>
       </c>
@@ -1161,7 +1155,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>45170.12499704861</v>
       </c>
@@ -1169,7 +1163,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>45170.166663657408</v>
       </c>
@@ -1177,7 +1171,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>45170.208330266207</v>
       </c>
@@ -1188,7 +1182,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>45170.249996874998</v>
       </c>
@@ -1199,7 +1193,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>45170.291663483797</v>
       </c>
@@ -1210,7 +1204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>45170.333330092595</v>
       </c>
@@ -1221,7 +1215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>45170.374996701386</v>
       </c>
@@ -1229,7 +1223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>45170.416663310185</v>
       </c>
@@ -1237,7 +1231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>45170.458329918984</v>
       </c>
@@ -1245,7 +1239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>45170.499996527775</v>
       </c>
@@ -1253,7 +1247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>45170.541663136573</v>
       </c>
@@ -1261,7 +1255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>45170.583329745372</v>
       </c>
@@ -1269,7 +1263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>45170.624996354163</v>
       </c>
@@ -1277,7 +1271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>45170.666662962962</v>
       </c>
@@ -1285,7 +1279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>45170.70832957176</v>
       </c>
@@ -1293,7 +1287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>45170.749996180559</v>
       </c>
@@ -1301,7 +1295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>45170.79166278935</v>
       </c>
@@ -1312,7 +1306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>45170.833329398149</v>
       </c>
@@ -1320,7 +1314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>45170.874996006947</v>
       </c>
@@ -1328,7 +1322,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>45170.916662615738</v>
       </c>
@@ -1336,7 +1330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>45170.958329224537</v>
       </c>
@@ -1344,7 +1338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>45170.999995833336</v>
       </c>
@@ -1355,7 +1349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>45171.041662442127</v>
       </c>
@@ -1366,7 +1360,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>45171.083329050925</v>
       </c>
@@ -1374,7 +1368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>45171.124995659724</v>
       </c>
@@ -1385,7 +1379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>45171.166662268515</v>
       </c>
@@ -1396,7 +1390,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>45171.208328877314</v>
       </c>
@@ -1404,7 +1398,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>45171.249995486112</v>
       </c>
@@ -1415,7 +1409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>45171.291662094911</v>
       </c>
@@ -1426,7 +1420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>45171.333328703702</v>
       </c>
@@ -1437,7 +1431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>45171.374995312501</v>
       </c>
@@ -1445,7 +1439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>45171.416661921299</v>
       </c>
@@ -1453,7 +1447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>45171.458328530091</v>
       </c>
@@ -1461,7 +1455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>45171.499995138889</v>
       </c>
@@ -1469,7 +1463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>45171.541661747688</v>
       </c>
@@ -1477,7 +1471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>45171.583328356479</v>
       </c>
@@ -1485,7 +1479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>45171.624994965277</v>
       </c>
@@ -1493,7 +1487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>45171.666661574076</v>
       </c>
@@ -1501,7 +1495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>45171.708328182867</v>
       </c>
@@ -1509,7 +1503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>45171.749994791666</v>
       </c>
@@ -1517,7 +1511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>45171.791661400464</v>
       </c>
@@ -1525,7 +1519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>45171.833328009256</v>
       </c>
@@ -1533,7 +1527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>45171.874994618054</v>
       </c>
@@ -1544,7 +1538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>45171.916661226853</v>
       </c>
@@ -1552,7 +1546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>45171.958327835651</v>
       </c>
@@ -1560,7 +1554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>45171.999994444443</v>
       </c>
@@ -1568,7 +1562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>45172.041661053241</v>
       </c>
@@ -1576,7 +1570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>45172.08332766204</v>
       </c>
@@ -1584,7 +1578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>45172.124994270831</v>
       </c>
@@ -1592,7 +1586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>45172.166666666664</v>
       </c>
@@ -1600,7 +1594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>45172.208339004632</v>
       </c>
@@ -1611,7 +1605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>45172.250011400465</v>
       </c>
@@ -1622,7 +1616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>45172.291683796298</v>
       </c>
@@ -1633,7 +1627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>45172.333356192132</v>
       </c>
@@ -1641,7 +1635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>45172.375028587965</v>
       </c>
@@ -1652,91 +1646,91 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>45172.416700983798</v>
       </c>
       <c r="B144" s="2"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>45172.458373379632</v>
       </c>
       <c r="B145" s="2"/>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>45172.500045775465</v>
       </c>
       <c r="B146" s="2"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>45172.541718171298</v>
       </c>
       <c r="B147" s="2"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>45172.583390567132</v>
       </c>
       <c r="B148" s="2"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>45172.625062962965</v>
       </c>
       <c r="B149" s="2"/>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>45172.666735358798</v>
       </c>
       <c r="B150" s="2"/>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>45172.708407754631</v>
       </c>
       <c r="B151" s="2"/>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>45172.750080150465</v>
       </c>
       <c r="B152" s="2"/>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>45172.791752546298</v>
       </c>
       <c r="B153" s="2"/>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>45172.833424942131</v>
       </c>
       <c r="B154" s="2"/>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>45172.875097337965</v>
       </c>
       <c r="B155" s="2"/>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>45172.916769733798</v>
       </c>
       <c r="B156" s="2"/>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>45172.958442129631</v>
       </c>
       <c r="B157" s="2"/>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>45173.000114525465</v>
       </c>
